--- a/testing/results_averitec_snippet/GPT_4/RARR_GPT_4_AVERITEC.xlsx
+++ b/testing/results_averitec_snippet/GPT_4/RARR_GPT_4_AVERITEC.xlsx
@@ -14,12 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="415">
   <si>
     <t>Statement</t>
-  </si>
-  <si>
-    <t>Name</t>
   </si>
   <si>
     <t>Original Veracity</t>
@@ -1651,22 +1648,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="94.14785714285713" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="6" width="13.005" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="6" width="13.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="6" width="13.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="13.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="13.005" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="13.005" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="7" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="13.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1685,7 +1681,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1694,15 +1690,14 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1715,29 +1710,28 @@
       <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>17</v>
@@ -1745,29 +1739,28 @@
       <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.2105263157894737</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="5">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0.2105263157894737</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>21</v>
@@ -1775,29 +1768,28 @@
       <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.1176470588235294</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="5">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0.1176470588235294</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1805,29 +1797,28 @@
       <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.3636363636363636</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="5">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="I5" s="4">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0.3636363636363636</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>29</v>
@@ -1835,29 +1826,28 @@
       <c r="F6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="5">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="5">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="I6" s="4">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0.2857142857142857</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
-      <c r="A7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>33</v>
@@ -1865,29 +1855,28 @@
       <c r="F7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.3529411764705883</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0.3529411764705883</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
-      <c r="A8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>37</v>
@@ -1895,29 +1884,28 @@
       <c r="F8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.7499999999999999</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="I8" s="4">
-        <v>1</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0.7499999999999999</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
-      <c r="A9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>41</v>
@@ -1925,26 +1913,25 @@
       <c r="F9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.3333333333333334</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="I9" s="4">
-        <v>1</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0.3333333333333334</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
-      <c r="A10" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>45</v>
@@ -1955,29 +1942,28 @@
       <c r="F10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
-      <c r="A11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>50</v>
@@ -1985,29 +1971,28 @@
       <c r="F11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
-      <c r="A12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>54</v>
@@ -2015,26 +2000,25 @@
       <c r="F12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.3333333333333334</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="I12" s="4">
-        <v>1</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0.3333333333333334</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>58</v>
@@ -2045,29 +2029,28 @@
       <c r="F13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="5">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="5">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
-      <c r="A14" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>63</v>
@@ -2075,29 +2058,28 @@
       <c r="F14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.7499999999999999</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="I14" s="4">
-        <v>1</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0.7499999999999999</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>67</v>
@@ -2105,29 +2087,28 @@
       <c r="F15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.1428571428571429</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H15" s="5">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="I15" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0.1428571428571429</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>71</v>
@@ -2135,29 +2116,28 @@
       <c r="F16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H16" s="4">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
-      <c r="A17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>75</v>
@@ -2165,29 +2145,28 @@
       <c r="F17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="5">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0.8536585365853658</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H17" s="5">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0.875</v>
-      </c>
-      <c r="J17" s="5">
-        <v>0.8536585365853658</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
-      <c r="A18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>79</v>
@@ -2195,29 +2174,28 @@
       <c r="F18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="H18" s="4">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
-      <c r="A19" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>83</v>
@@ -2225,29 +2203,28 @@
       <c r="F19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="H19" s="4">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0.888888888888889</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="I19" s="4">
-        <v>1</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0.888888888888889</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
-      <c r="A20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>87</v>
@@ -2255,8 +2232,8 @@
       <c r="F20" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>89</v>
+      <c r="G20" s="5">
+        <v>0.5</v>
       </c>
       <c r="H20" s="5">
         <v>0.5</v>
@@ -2264,20 +2241,19 @@
       <c r="I20" s="5">
         <v>0.5</v>
       </c>
-      <c r="J20" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="3"/>
+        <v>89</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>91</v>
@@ -2285,29 +2261,28 @@
       <c r="F21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H21" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J21" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
-      <c r="A22" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>95</v>
@@ -2315,29 +2290,28 @@
       <c r="F22" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H22" s="4">
-        <v>0</v>
-      </c>
-      <c r="I22" s="4">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>99</v>
@@ -2345,29 +2319,28 @@
       <c r="F23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+      <c r="A24" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="4">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
-      <c r="A24" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>103</v>
@@ -2375,29 +2348,28 @@
       <c r="F24" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>105</v>
+      <c r="G24" s="5">
+        <v>0.6</v>
       </c>
       <c r="H24" s="5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I24" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J24" s="5">
         <v>0.5454545454545454</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
       <c r="A25" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>107</v>
@@ -2405,29 +2377,28 @@
       <c r="F25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H25" s="5">
+      <c r="G25" s="5">
         <v>0.4444444444444444</v>
       </c>
-      <c r="I25" s="4">
+      <c r="H25" s="4">
         <v>1</v>
       </c>
-      <c r="J25" s="5">
+      <c r="I25" s="5">
         <v>0.6153846153846153</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
       <c r="A26" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>111</v>
@@ -2435,29 +2406,28 @@
       <c r="F26" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="H26" s="5">
+      <c r="G26" s="5">
         <v>0.875</v>
       </c>
-      <c r="I26" s="4">
+      <c r="H26" s="4">
         <v>1</v>
       </c>
-      <c r="J26" s="5">
+      <c r="I26" s="5">
         <v>0.9333333333333333</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18">
       <c r="A27" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>115</v>
@@ -2465,8 +2435,8 @@
       <c r="F27" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>117</v>
+      <c r="G27" s="5">
+        <v>0.5</v>
       </c>
       <c r="H27" s="5">
         <v>0.5</v>
@@ -2474,20 +2444,19 @@
       <c r="I27" s="5">
         <v>0.5</v>
       </c>
-      <c r="J27" s="5">
-        <v>0.5</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18">
       <c r="A28" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B28" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C28" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>119</v>
@@ -2495,29 +2464,28 @@
       <c r="F28" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="5">
+      <c r="G28" s="5">
         <v>0.75</v>
       </c>
-      <c r="I28" s="4">
+      <c r="H28" s="4">
         <v>1</v>
       </c>
-      <c r="J28" s="5">
+      <c r="I28" s="5">
         <v>0.8571428571428571</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
       <c r="A29" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>123</v>
@@ -2525,29 +2493,28 @@
       <c r="F29" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H29" s="4">
+      <c r="G29" s="4">
         <v>1</v>
       </c>
+      <c r="H29" s="5">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="I29" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="J29" s="5">
         <v>0.8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
       <c r="A30" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>127</v>
@@ -2555,29 +2522,28 @@
       <c r="F30" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H30" s="5">
+      <c r="G30" s="5">
         <v>0.2222222222222222</v>
       </c>
-      <c r="I30" s="4">
+      <c r="H30" s="4">
         <v>1</v>
       </c>
-      <c r="J30" s="5">
+      <c r="I30" s="5">
         <v>0.3636363636363636</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18">
       <c r="A31" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B31" s="3"/>
+        <v>129</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C31" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>131</v>
@@ -2585,29 +2551,28 @@
       <c r="F31" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H31" s="5">
+      <c r="G31" s="5">
         <v>0.1666666666666667</v>
       </c>
-      <c r="I31" s="4">
+      <c r="H31" s="4">
         <v>1</v>
       </c>
-      <c r="J31" s="5">
+      <c r="I31" s="5">
         <v>0.2857142857142857</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18">
       <c r="A32" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>135</v>
@@ -2615,29 +2580,28 @@
       <c r="F32" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>137</v>
+      <c r="G32" s="5">
+        <v>0.1666666666666667</v>
       </c>
       <c r="H32" s="5">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="I32" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="J32" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18">
       <c r="A33" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B33" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>139</v>
@@ -2645,29 +2609,28 @@
       <c r="F33" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>141</v>
+      <c r="G33" s="4">
+        <v>0</v>
       </c>
       <c r="H33" s="4">
         <v>0</v>
       </c>
       <c r="I33" s="4">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18">
       <c r="A34" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B34" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C34" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>143</v>
@@ -2675,59 +2638,57 @@
       <c r="F34" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>145</v>
+      <c r="G34" s="5">
+        <v>0.8</v>
       </c>
       <c r="H34" s="5">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="I34" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="J34" s="5">
         <v>0.7741935483870969</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18">
       <c r="A35" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B35" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>148</v>
+      <c r="G35" s="4">
+        <v>0</v>
       </c>
       <c r="H35" s="4">
         <v>0</v>
       </c>
       <c r="I35" s="4">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18">
       <c r="A36" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B36" s="3"/>
+        <v>148</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>150</v>
@@ -2735,29 +2696,28 @@
       <c r="F36" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H36" s="5">
+      <c r="G36" s="5">
         <v>0.7142857142857143</v>
       </c>
-      <c r="I36" s="4">
+      <c r="H36" s="4">
         <v>1</v>
       </c>
-      <c r="J36" s="5">
+      <c r="I36" s="5">
         <v>0.8333333333333333</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18">
       <c r="A37" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>154</v>
@@ -2765,29 +2725,28 @@
       <c r="F37" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>156</v>
+      <c r="G37" s="5">
+        <v>0.125</v>
       </c>
       <c r="H37" s="5">
-        <v>0.125</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I37" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J37" s="5">
         <v>0.1818181818181818</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18">
       <c r="A38" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="3"/>
+        <v>156</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>158</v>
@@ -2795,29 +2754,28 @@
       <c r="F38" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>160</v>
+      <c r="G38" s="5">
+        <v>0.4</v>
       </c>
       <c r="H38" s="5">
         <v>0.4</v>
       </c>
       <c r="I38" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J38" s="5">
         <v>0.4000000000000001</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18">
       <c r="A39" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B39" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>162</v>
@@ -2825,29 +2783,28 @@
       <c r="F39" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>164</v>
+      <c r="G39" s="5">
+        <v>0.5</v>
       </c>
       <c r="H39" s="5">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I39" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J39" s="5">
         <v>0.4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18">
       <c r="A40" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B40" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C40" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>166</v>
@@ -2855,29 +2812,28 @@
       <c r="F40" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H40" s="5">
+      <c r="G40" s="5">
         <v>0.625</v>
       </c>
-      <c r="I40" s="4">
+      <c r="H40" s="4">
         <v>1</v>
       </c>
-      <c r="J40" s="5">
+      <c r="I40" s="5">
         <v>0.7692307692307693</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18">
       <c r="A41" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B41" s="3"/>
+        <v>168</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>170</v>
@@ -2885,29 +2841,28 @@
       <c r="F41" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>172</v>
+      <c r="G41" s="5">
+        <v>0.6666666666666666</v>
       </c>
       <c r="H41" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="I41" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J41" s="5">
         <v>0.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18">
       <c r="A42" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>174</v>
@@ -2915,8 +2870,8 @@
       <c r="F42" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>176</v>
+      <c r="G42" s="5">
+        <v>0.25</v>
       </c>
       <c r="H42" s="5">
         <v>0.25</v>
@@ -2924,20 +2879,19 @@
       <c r="I42" s="5">
         <v>0.25</v>
       </c>
-      <c r="J42" s="5">
-        <v>0.25</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18">
       <c r="A43" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>178</v>
@@ -2945,29 +2899,28 @@
       <c r="F43" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>180</v>
+      <c r="G43" s="4">
+        <v>1</v>
       </c>
       <c r="H43" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="4">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18">
       <c r="A44" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>182</v>
@@ -2975,29 +2928,28 @@
       <c r="F44" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>184</v>
+      <c r="G44" s="5">
+        <v>0.0625</v>
       </c>
       <c r="H44" s="5">
-        <v>0.0625</v>
+        <v>0.25</v>
       </c>
       <c r="I44" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="J44" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18">
       <c r="A45" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B45" s="3"/>
+        <v>184</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>12</v>
+        <v>185</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>186</v>
@@ -3005,29 +2957,28 @@
       <c r="F45" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>188</v>
+      <c r="G45" s="5">
+        <v>0.8333333333333334</v>
       </c>
       <c r="H45" s="5">
-        <v>0.8333333333333334</v>
+        <v>0.4</v>
       </c>
       <c r="I45" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J45" s="5">
         <v>0.5405405405405406</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18">
       <c r="A46" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>190</v>
@@ -3035,29 +2986,28 @@
       <c r="F46" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>192</v>
+      <c r="G46" s="5">
+        <v>0.1428571428571428</v>
       </c>
       <c r="H46" s="5">
-        <v>0.1428571428571428</v>
+        <v>0.25</v>
       </c>
       <c r="I46" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="J46" s="5">
         <v>0.1818181818181818</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18">
       <c r="A47" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>194</v>
@@ -3065,29 +3015,28 @@
       <c r="F47" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>196</v>
+      <c r="G47" s="5">
+        <v>0.2</v>
       </c>
       <c r="H47" s="5">
-        <v>0.2</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I47" s="5">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="J47" s="5">
         <v>0.2727272727272728</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18">
       <c r="A48" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B48" s="3"/>
+        <v>196</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>198</v>
@@ -3095,26 +3044,25 @@
       <c r="F48" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>200</v>
+      <c r="G48" s="5">
+        <v>0.09090909090909091</v>
       </c>
       <c r="H48" s="5">
-        <v>0.09090909090909091</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I48" s="5">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="J48" s="5">
         <v>0.1379310344827586</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18">
       <c r="A49" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>202</v>
@@ -3125,29 +3073,28 @@
       <c r="F49" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="H49" s="5">
+      <c r="G49" s="5">
         <v>0.3333333333333333</v>
       </c>
-      <c r="I49" s="4">
+      <c r="H49" s="4">
         <v>1</v>
       </c>
-      <c r="J49" s="5">
+      <c r="I49" s="5">
         <v>0.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18">
       <c r="A50" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B50" s="3"/>
+        <v>205</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C50" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>207</v>
@@ -3155,29 +3102,28 @@
       <c r="F50" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="H50" s="5">
+      <c r="G50" s="5">
         <v>0.5</v>
       </c>
-      <c r="I50" s="4">
+      <c r="H50" s="4">
         <v>1</v>
       </c>
-      <c r="J50" s="5">
+      <c r="I50" s="5">
         <v>0.6666666666666666</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18">
       <c r="A51" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>211</v>
@@ -3185,29 +3131,28 @@
       <c r="F51" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H51" s="5">
+      <c r="G51" s="5">
         <v>0.4</v>
       </c>
-      <c r="I51" s="4">
+      <c r="H51" s="4">
         <v>1</v>
       </c>
-      <c r="J51" s="5">
+      <c r="I51" s="5">
         <v>0.5714285714285715</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18">
       <c r="A52" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B52" s="3"/>
+        <v>213</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="C52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>216</v>
@@ -3215,29 +3160,28 @@
       <c r="F52" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="H52" s="5">
+      <c r="G52" s="5">
         <v>0.6666666666666666</v>
       </c>
+      <c r="H52" s="4">
+        <v>0</v>
+      </c>
       <c r="I52" s="4">
-        <v>0</v>
-      </c>
-      <c r="J52" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18">
       <c r="A53" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>220</v>
@@ -3245,29 +3189,28 @@
       <c r="F53" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="H53" s="5">
+      <c r="G53" s="5">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I53" s="4">
+      <c r="H53" s="4">
         <v>1</v>
       </c>
-      <c r="J53" s="5">
+      <c r="I53" s="5">
         <v>0.8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18">
       <c r="A54" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>224</v>
@@ -3275,29 +3218,28 @@
       <c r="F54" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>226</v>
+      <c r="G54" s="5">
+        <v>0.2</v>
       </c>
       <c r="H54" s="5">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I54" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J54" s="5">
         <v>0.25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18">
       <c r="A55" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>228</v>
@@ -3305,29 +3247,28 @@
       <c r="F55" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="H55" s="4">
-        <v>0</v>
-      </c>
-      <c r="I55" s="5">
+      <c r="G55" s="4">
+        <v>0</v>
+      </c>
+      <c r="H55" s="5">
         <v>0.5</v>
       </c>
-      <c r="J55" s="4">
+      <c r="I55" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18">
       <c r="A56" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>232</v>
@@ -3335,29 +3276,28 @@
       <c r="F56" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>234</v>
+      <c r="G56" s="4">
+        <v>0</v>
       </c>
       <c r="H56" s="4">
         <v>0</v>
       </c>
       <c r="I56" s="4">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18">
       <c r="A57" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>236</v>
@@ -3365,29 +3305,28 @@
       <c r="F57" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>238</v>
+      <c r="G57" s="4">
+        <v>0</v>
       </c>
       <c r="H57" s="4">
         <v>0</v>
       </c>
       <c r="I57" s="4">
-        <v>0</v>
-      </c>
-      <c r="J57" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18">
       <c r="A58" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>240</v>
@@ -3395,29 +3334,28 @@
       <c r="F58" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>242</v>
+      <c r="G58" s="5">
+        <v>0.6666666666666666</v>
       </c>
       <c r="H58" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="I58" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J58" s="5">
         <v>0.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18">
       <c r="A59" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>244</v>
@@ -3425,29 +3363,28 @@
       <c r="F59" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>246</v>
+      <c r="G59" s="5">
+        <v>0.1666666666666667</v>
       </c>
       <c r="H59" s="5">
-        <v>0.1666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I59" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="J59" s="5">
         <v>0.2666666666666667</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18">
       <c r="A60" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>248</v>
@@ -3455,29 +3392,28 @@
       <c r="F60" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>250</v>
+      <c r="G60" s="4">
+        <v>0</v>
       </c>
       <c r="H60" s="4">
         <v>0</v>
       </c>
       <c r="I60" s="4">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18">
       <c r="A61" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>252</v>
@@ -3485,29 +3421,28 @@
       <c r="F61" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>254</v>
+      <c r="G61" s="5">
+        <v>0.2</v>
       </c>
       <c r="H61" s="5">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I61" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J61" s="5">
         <v>0.2857142857142858</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18">
       <c r="A62" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>256</v>
@@ -3515,29 +3450,28 @@
       <c r="F62" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>258</v>
+      <c r="G62" s="5">
+        <v>0.4</v>
       </c>
       <c r="H62" s="5">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I62" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J62" s="5">
         <v>0.4444444444444445</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
       <c r="A63" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>260</v>
@@ -3545,29 +3479,28 @@
       <c r="F63" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>262</v>
+      <c r="G63" s="4">
+        <v>0</v>
       </c>
       <c r="H63" s="4">
         <v>0</v>
       </c>
       <c r="I63" s="4">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>264</v>
@@ -3575,29 +3508,28 @@
       <c r="F64" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>266</v>
+      <c r="G64" s="5">
+        <v>0.2</v>
       </c>
       <c r="H64" s="5">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I64" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J64" s="5">
         <v>0.2857142857142858</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>268</v>
@@ -3605,8 +3537,8 @@
       <c r="F65" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>270</v>
+      <c r="G65" s="5">
+        <v>0.1428571428571428</v>
       </c>
       <c r="H65" s="5">
         <v>0.1428571428571428</v>
@@ -3614,20 +3546,19 @@
       <c r="I65" s="5">
         <v>0.1428571428571428</v>
       </c>
-      <c r="J65" s="5">
-        <v>0.1428571428571428</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>272</v>
@@ -3635,29 +3566,28 @@
       <c r="F66" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>274</v>
+      <c r="G66" s="4">
+        <v>0</v>
       </c>
       <c r="H66" s="4">
         <v>0</v>
       </c>
       <c r="I66" s="4">
-        <v>0</v>
-      </c>
-      <c r="J66" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
       <c r="A67" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>276</v>
@@ -3665,29 +3595,28 @@
       <c r="F67" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>278</v>
+      <c r="G67" s="4">
+        <v>0</v>
       </c>
       <c r="H67" s="4">
         <v>0</v>
       </c>
       <c r="I67" s="4">
-        <v>0</v>
-      </c>
-      <c r="J67" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>280</v>
@@ -3695,29 +3624,28 @@
       <c r="F68" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>282</v>
+      <c r="G68" s="5">
+        <v>0.25</v>
       </c>
       <c r="H68" s="5">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I68" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J68" s="5">
         <v>0.3333333333333333</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
       <c r="A69" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>284</v>
@@ -3725,29 +3653,28 @@
       <c r="F69" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>286</v>
+      <c r="G69" s="5">
+        <v>0.125</v>
       </c>
       <c r="H69" s="5">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="I69" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J69" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>288</v>
@@ -3755,29 +3682,28 @@
       <c r="F70" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="H70" s="5">
+      <c r="G70" s="5">
         <v>0.5</v>
       </c>
-      <c r="I70" s="4">
+      <c r="H70" s="4">
         <v>1</v>
       </c>
-      <c r="J70" s="5">
+      <c r="I70" s="5">
         <v>0.6666666666666666</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
       <c r="A71" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>292</v>
@@ -3785,29 +3711,28 @@
       <c r="F71" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>294</v>
+      <c r="G71" s="4">
+        <v>0</v>
       </c>
       <c r="H71" s="4">
         <v>0</v>
       </c>
       <c r="I71" s="4">
-        <v>0</v>
-      </c>
-      <c r="J71" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>296</v>
@@ -3815,29 +3740,28 @@
       <c r="F72" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>298</v>
+      <c r="G72" s="4">
+        <v>0</v>
       </c>
       <c r="H72" s="4">
         <v>0</v>
       </c>
       <c r="I72" s="4">
-        <v>0</v>
-      </c>
-      <c r="J72" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
       <c r="A73" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>300</v>
@@ -3845,29 +3769,28 @@
       <c r="F73" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>302</v>
+      <c r="G73" s="5">
+        <v>0.25</v>
       </c>
       <c r="H73" s="5">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I73" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J73" s="5">
         <v>0.3333333333333333</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>304</v>
@@ -3875,29 +3798,28 @@
       <c r="F74" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>306</v>
+      <c r="G74" s="5">
+        <v>0.2</v>
       </c>
       <c r="H74" s="5">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I74" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J74" s="5">
         <v>0.25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>308</v>
@@ -3905,29 +3827,28 @@
       <c r="F75" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>310</v>
+      <c r="G75" s="5">
+        <v>0.1875</v>
       </c>
       <c r="H75" s="5">
-        <v>0.1875</v>
+        <v>0.4</v>
       </c>
       <c r="I75" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J75" s="5">
         <v>0.2553191489361702</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>312</v>
@@ -3935,29 +3856,28 @@
       <c r="F76" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>314</v>
+      <c r="G76" s="5">
+        <v>0.5454545454545454</v>
       </c>
       <c r="H76" s="5">
-        <v>0.5454545454545454</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I76" s="5">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="J76" s="5">
         <v>0.1846153846153846</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>316</v>
@@ -3965,29 +3885,28 @@
       <c r="F77" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>318</v>
+      <c r="G77" s="4">
+        <v>0.33333</v>
       </c>
       <c r="H77" s="4">
-        <v>0.33333</v>
+        <v>0.71</v>
       </c>
       <c r="I77" s="4">
-        <v>0.71</v>
-      </c>
-      <c r="J77" s="4">
         <v>0.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>320</v>
@@ -3995,29 +3914,28 @@
       <c r="F78" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>322</v>
+      <c r="G78" s="5">
+        <v>0.2</v>
       </c>
       <c r="H78" s="5">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I78" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J78" s="5">
         <v>0.25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>324</v>
@@ -4025,29 +3943,28 @@
       <c r="F79" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>326</v>
+      <c r="G79" s="4">
+        <v>0</v>
       </c>
       <c r="H79" s="4">
         <v>0</v>
       </c>
       <c r="I79" s="4">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>328</v>
@@ -4055,29 +3972,28 @@
       <c r="F80" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>330</v>
+      <c r="G80" s="5">
+        <v>0.3333333333333333</v>
       </c>
       <c r="H80" s="5">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="I80" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J80" s="5">
         <v>0.4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
       <c r="A81" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>332</v>
@@ -4085,29 +4001,28 @@
       <c r="F81" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>334</v>
+      <c r="G81" s="5">
+        <v>0.8333333333333334</v>
       </c>
       <c r="H81" s="5">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="I81" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="J81" s="5">
         <v>0.816326530612245</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>336</v>
@@ -4115,29 +4030,28 @@
       <c r="F82" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H82" s="5">
+      <c r="G82" s="5">
         <v>0.1111111111111111</v>
       </c>
-      <c r="I82" s="4">
+      <c r="H82" s="4">
         <v>1</v>
       </c>
-      <c r="J82" s="5">
+      <c r="I82" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
       <c r="A83" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>340</v>
@@ -4145,29 +4059,28 @@
       <c r="F83" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>342</v>
+      <c r="G83" s="5">
+        <v>0.5</v>
       </c>
       <c r="H83" s="5">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I83" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="J83" s="5">
         <v>0.5714285714285715</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
       <c r="A84" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>344</v>
@@ -4175,29 +4088,28 @@
       <c r="F84" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="H84" s="5">
+      <c r="G84" s="5">
         <v>0.2142857142857143</v>
       </c>
-      <c r="I84" s="4">
+      <c r="H84" s="4">
         <v>1</v>
       </c>
-      <c r="J84" s="5">
+      <c r="I84" s="5">
         <v>0.3529411764705883</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18">
       <c r="A85" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>348</v>
@@ -4205,29 +4117,28 @@
       <c r="F85" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>350</v>
+      <c r="G85" s="5">
+        <v>0.5</v>
       </c>
       <c r="H85" s="5">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I85" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J85" s="5">
         <v>0.4444444444444445</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18">
       <c r="A86" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>352</v>
@@ -4235,29 +4146,28 @@
       <c r="F86" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>354</v>
+      <c r="G86" s="4">
+        <v>0</v>
       </c>
       <c r="H86" s="4">
         <v>0</v>
       </c>
       <c r="I86" s="4">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18">
       <c r="A87" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>356</v>
@@ -4265,8 +4175,8 @@
       <c r="F87" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>358</v>
+      <c r="G87" s="5">
+        <v>0.1666666666666667</v>
       </c>
       <c r="H87" s="5">
         <v>0.1666666666666667</v>
@@ -4274,20 +4184,19 @@
       <c r="I87" s="5">
         <v>0.1666666666666667</v>
       </c>
-      <c r="J87" s="5">
-        <v>0.1666666666666667</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18">
       <c r="A88" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>359</v>
-      </c>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>360</v>
@@ -4295,29 +4204,28 @@
       <c r="F88" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>362</v>
+      <c r="G88" s="4">
+        <v>0</v>
       </c>
       <c r="H88" s="4">
         <v>0</v>
       </c>
       <c r="I88" s="4">
-        <v>0</v>
-      </c>
-      <c r="J88" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18">
       <c r="A89" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>364</v>
@@ -4325,29 +4233,28 @@
       <c r="F89" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>366</v>
+      <c r="G89" s="5">
+        <v>0.6666666666666666</v>
       </c>
       <c r="H89" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I89" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J89" s="5">
         <v>0.4444444444444444</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18">
       <c r="A90" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>368</v>
@@ -4355,29 +4262,28 @@
       <c r="F90" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="H90" s="5">
+      <c r="G90" s="5">
         <v>0.4285714285714285</v>
       </c>
-      <c r="I90" s="4">
+      <c r="H90" s="4">
         <v>1</v>
       </c>
-      <c r="J90" s="5">
+      <c r="I90" s="5">
         <v>0.6</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18">
       <c r="A91" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>372</v>
@@ -4385,29 +4291,28 @@
       <c r="F91" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>374</v>
+      <c r="G91" s="4">
+        <v>0</v>
       </c>
       <c r="H91" s="4">
         <v>0</v>
       </c>
       <c r="I91" s="4">
-        <v>0</v>
-      </c>
-      <c r="J91" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18">
       <c r="A92" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>376</v>
@@ -4415,29 +4320,28 @@
       <c r="F92" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="H92" s="4">
-        <v>0</v>
-      </c>
-      <c r="I92" s="5">
+      <c r="G92" s="4">
+        <v>0</v>
+      </c>
+      <c r="H92" s="5">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J92" s="4">
+      <c r="I92" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18">
       <c r="A93" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>380</v>
@@ -4445,29 +4349,28 @@
       <c r="F93" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="G93" s="3" t="s">
-        <v>382</v>
+      <c r="G93" s="4">
+        <v>0</v>
       </c>
       <c r="H93" s="4">
         <v>0</v>
       </c>
       <c r="I93" s="4">
-        <v>0</v>
-      </c>
-      <c r="J93" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18">
       <c r="A94" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>383</v>
-      </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>384</v>
@@ -4475,29 +4378,28 @@
       <c r="F94" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="H94" s="5">
+      <c r="G94" s="5">
         <v>0.125</v>
       </c>
-      <c r="I94" s="4">
+      <c r="H94" s="4">
         <v>1</v>
       </c>
-      <c r="J94" s="5">
+      <c r="I94" s="5">
         <v>0.2222222222222222</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18">
       <c r="A95" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>388</v>
@@ -4505,29 +4407,28 @@
       <c r="F95" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>390</v>
+      <c r="G95" s="4">
+        <v>0</v>
       </c>
       <c r="H95" s="4">
         <v>0</v>
       </c>
       <c r="I95" s="4">
-        <v>0</v>
-      </c>
-      <c r="J95" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18">
       <c r="A96" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>392</v>
@@ -4535,29 +4436,28 @@
       <c r="F96" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="H96" s="5">
+      <c r="G96" s="5">
         <v>0.3333333333333333</v>
       </c>
-      <c r="I96" s="4">
+      <c r="H96" s="4">
         <v>1</v>
       </c>
-      <c r="J96" s="5">
+      <c r="I96" s="5">
         <v>0.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18">
       <c r="A97" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>395</v>
-      </c>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>396</v>
@@ -4565,29 +4465,28 @@
       <c r="F97" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="G97" s="3" t="s">
-        <v>398</v>
+      <c r="G97" s="5">
+        <v>0.5714285714285714</v>
       </c>
       <c r="H97" s="5">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I97" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="J97" s="5">
         <v>0.6153846153846153</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18">
       <c r="A98" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>400</v>
@@ -4595,8 +4494,8 @@
       <c r="F98" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>402</v>
+      <c r="G98" s="5">
+        <v>0.5</v>
       </c>
       <c r="H98" s="5">
         <v>0.5</v>
@@ -4604,20 +4503,19 @@
       <c r="I98" s="5">
         <v>0.5</v>
       </c>
-      <c r="J98" s="5">
-        <v>0.5</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18">
       <c r="A99" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>404</v>
@@ -4625,29 +4523,28 @@
       <c r="F99" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>406</v>
+      <c r="G99" s="4">
+        <v>0</v>
       </c>
       <c r="H99" s="4">
         <v>0</v>
       </c>
       <c r="I99" s="4">
-        <v>0</v>
-      </c>
-      <c r="J99" s="4">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18">
       <c r="A100" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>408</v>
@@ -4655,26 +4552,25 @@
       <c r="F100" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>410</v>
+      <c r="G100" s="5">
+        <v>0.5555555555555556</v>
       </c>
       <c r="H100" s="5">
-        <v>0.5555555555555556</v>
+        <v>0.375</v>
       </c>
       <c r="I100" s="5">
-        <v>0.375</v>
-      </c>
-      <c r="J100" s="5">
         <v>0.4477611940298508</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18">
       <c r="A101" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>412</v>
@@ -4685,16 +4581,13 @@
       <c r="F101" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>415</v>
+      <c r="G101" s="5">
+        <v>0.2857142857142857</v>
       </c>
       <c r="H101" s="5">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I101" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J101" s="5">
         <v>0.3076923076923077</v>
       </c>
     </row>
